--- a/bird_ic_lora_dataset.xlsx
+++ b/bird_ic_lora_dataset.xlsx
@@ -7,15 +7,17 @@
     <sheet name="Pairing rules" sheetId="3" r:id="rId4"/>
     <sheet name="Empty Sky Clips" sheetId="4" r:id="rId5"/>
     <sheet name="House Rooms" sheetId="5" r:id="rId6"/>
-    <sheet name="Browse more" sheetId="6" r:id="rId7"/>
-    <sheet name="Training pairs" sheetId="7" r:id="rId8"/>
+    <sheet name="Bird videos (sky / flying)" sheetId="6" r:id="rId7"/>
+    <sheet name="Bird videos (parrot / cage)" sheetId="7" r:id="rId8"/>
+    <sheet name="Browse more" sheetId="8" r:id="rId9"/>
+    <sheet name="Training pairs" sheetId="9" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -26,14 +28,8 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -46,14 +42,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F1FA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -61,36 +51,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBDD7EE"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBDD7EE"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBDD7EE"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBDD7EE"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyAlignment="1" applyBorder="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
-      <alignment wrapText="1" vertical="center" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1" vertical="center"/>
     </xf>
   </cellXfs>
@@ -101,16 +70,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="80" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bird IC-LoRA dataset tracker</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird IC-LoRA dataset</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -119,7 +88,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Created</t>
+          <t xml:space="preserve">Updated</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
@@ -131,208 +100,28 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Open the HTML page for clickable links.</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">How to open this in Google Sheets</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Go to https://drive.google.com</t>
-        </is>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2. Upload bird_ic_lora_dataset.xlsx</t>
-        </is>
-      </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. Right-click the file -&gt; Open with -&gt; Google Sheets</t>
-        </is>
-      </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Or: https://sheets.new  then File -&gt; Import -&gt; Upload this file -&gt; Replace spreadsheet</t>
-        </is>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tabs</t>
-        </is>
-      </c>
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">How to collect</t>
-        </is>
-      </c>
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">What data you need and pairing rules</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Empty Sky Clips</t>
-        </is>
-      </c>
-      <c r="B12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Direct download links for sky with no birds</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">House Rooms</t>
-        </is>
-      </c>
-      <c r="B13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Direct download links for indoor rooms (bird goes inside)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Browse more</t>
-        </is>
-      </c>
-      <c r="B14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Search pages with hundreds more clips</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Training pairs</t>
-        </is>
-      </c>
-      <c r="B15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">How sky and room clips connect as IC-LoRA pairs</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B16" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IC-LoRA reminder</t>
-        </is>
-      </c>
-      <c r="B17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reference = empty scene. Target = same scene with the bird. Same length and resolution.</t>
-        </is>
-      </c>
-      <c r="B18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:B3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="70" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -499,15 +288,14 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E6"/>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="90" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -566,7 +354,7 @@
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">People, text, watermarks, other animals, or a bird already in the sky</t>
+          <t xml:space="preserve">People, text, watermarks, other animals (unless that is the bird you want)</t>
         </is>
       </c>
     </row>
@@ -602,25 +390,23 @@
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rare on stock sites. Film a pet/stuffed bird, composite a bird onto empty rooms, or search parrot indoor / budgie living room / bird on window sill</t>
+          <t xml:space="preserve">True house-interior bird clips are rare. Use cage/pet parrot clips, film a pet bird, or composite a bird onto empty rooms</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B8"/>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="48" customWidth="1"/>
-    <col min="4" max="4" width="70" customWidth="1"/>
-    <col min="5" max="5" width="36" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -649,15 +435,12 @@
           <t xml:space="preserve">Use as</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Downloaded?</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="0">
-        <v>1</v>
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
@@ -669,7 +452,7 @@
           <t xml:space="preserve">Cloudy sky timelapse</t>
         </is>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/time-lapse-video-of-a-cloudy-sky-284/","https://mixkit.co/free-stock-video/time-lapse-video-of-a-cloudy-sky-284/")</f>
       </c>
       <c r="E2" s="0" t="inlineStr">
@@ -677,15 +460,12 @@
           <t xml:space="preserve">Outdoor reference (empty sky)</t>
         </is>
       </c>
-      <c r="F2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="0">
-        <v>2</v>
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
@@ -697,7 +477,7 @@
           <t xml:space="preserve">Sky timelapse, moving clouds</t>
         </is>
       </c>
-      <c r="D3" s="3" t="str">
+      <c r="D3" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/sky-time-lapse-1905/","https://mixkit.co/free-stock-video/sky-time-lapse-1905/")</f>
       </c>
       <c r="E3" s="0" t="inlineStr">
@@ -705,15 +485,12 @@
           <t xml:space="preserve">Outdoor reference (empty sky)</t>
         </is>
       </c>
-      <c r="F3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="0">
-        <v>3</v>
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
@@ -725,7 +502,7 @@
           <t xml:space="preserve">White clouds on clear blue sky</t>
         </is>
       </c>
-      <c r="D4" s="3" t="str">
+      <c r="D4" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/white-clouds-moving-across-a-clear-blue-sky-51102/","https://mixkit.co/free-stock-video/white-clouds-moving-across-a-clear-blue-sky-51102/")</f>
       </c>
       <c r="E4" s="0" t="inlineStr">
@@ -733,15 +510,12 @@
           <t xml:space="preserve">Outdoor reference (empty sky)</t>
         </is>
       </c>
-      <c r="F4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="0">
-        <v>4</v>
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
@@ -753,7 +527,7 @@
           <t xml:space="preserve">White clouds moving quickly</t>
         </is>
       </c>
-      <c r="D5" s="3" t="str">
+      <c r="D5" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/white-clouds-moving-across-a-clear-blue-sky-quickly-51105/","https://mixkit.co/free-stock-video/white-clouds-moving-across-a-clear-blue-sky-quickly-51105/")</f>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -761,15 +535,12 @@
           <t xml:space="preserve">Outdoor reference (empty sky)</t>
         </is>
       </c>
-      <c r="F5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="0">
-        <v>5</v>
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
@@ -781,7 +552,7 @@
           <t xml:space="preserve">Fluffy clouds, bright blue sky (4K)</t>
         </is>
       </c>
-      <c r="D6" s="3" t="str">
+      <c r="D6" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/fluffy-clouds-against-a-bright-blue-sky-100715/","https://mixkit.co/free-stock-video/fluffy-clouds-against-a-bright-blue-sky-100715/")</f>
       </c>
       <c r="E6" s="0" t="inlineStr">
@@ -789,15 +560,12 @@
           <t xml:space="preserve">Outdoor reference (empty sky)</t>
         </is>
       </c>
-      <c r="F6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="0">
-        <v>6</v>
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
@@ -809,7 +577,7 @@
           <t xml:space="preserve">Fluffy clouds, open sky</t>
         </is>
       </c>
-      <c r="D7" s="3" t="str">
+      <c r="D7" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/fluffy-clouds-floating-gently-across-a-great-blue-open-sky-44967/","https://mixkit.co/free-stock-video/fluffy-clouds-floating-gently-across-a-great-blue-open-sky-44967/")</f>
       </c>
       <c r="E7" s="0" t="inlineStr">
@@ -817,15 +585,12 @@
           <t xml:space="preserve">Outdoor reference (empty sky)</t>
         </is>
       </c>
-      <c r="F7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="0">
-        <v>7</v>
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
@@ -837,7 +602,7 @@
           <t xml:space="preserve">Blue sky, wind-blown clouds</t>
         </is>
       </c>
-      <c r="D8" s="3" t="str">
+      <c r="D8" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/blue-sky-background-as-the-clouds-travel-blown-by-the-26108/","https://mixkit.co/free-stock-video/blue-sky-background-as-the-clouds-travel-blown-by-the-26108/")</f>
       </c>
       <c r="E8" s="0" t="inlineStr">
@@ -845,15 +610,12 @@
           <t xml:space="preserve">Outdoor reference (empty sky)</t>
         </is>
       </c>
-      <c r="F8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="0">
-        <v>8</v>
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
@@ -865,7 +627,7 @@
           <t xml:space="preserve">Sun + thin clouds timelapse</t>
         </is>
       </c>
-      <c r="D9" s="3" t="str">
+      <c r="D9" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/sky-view-with-sun-and-clouds-in-a-timelapse-50160/","https://mixkit.co/free-stock-video/sky-view-with-sun-and-clouds-in-a-timelapse-50160/")</f>
       </c>
       <c r="E9" s="0" t="inlineStr">
@@ -873,15 +635,12 @@
           <t xml:space="preserve">Outdoor reference (empty sky)</t>
         </is>
       </c>
-      <c r="F9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="0">
-        <v>9</v>
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
@@ -893,7 +652,7 @@
           <t xml:space="preserve">Clouds moving across blue sky</t>
         </is>
       </c>
-      <c r="D10" s="3" t="str">
+      <c r="D10" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/timelapse-of-clouds-moving-across-a-blue-sky-45272/","https://mixkit.co/free-stock-video/timelapse-of-clouds-moving-across-a-blue-sky-45272/")</f>
       </c>
       <c r="E10" s="0" t="inlineStr">
@@ -901,15 +660,12 @@
           <t xml:space="preserve">Outdoor reference (empty sky)</t>
         </is>
       </c>
-      <c r="F10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="0">
-        <v>10</v>
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
@@ -921,7 +677,7 @@
           <t xml:space="preserve">Clouds passing across the sun</t>
         </is>
       </c>
-      <c r="D11" s="3" t="str">
+      <c r="D11" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/clouds-passing-across-the-sun-20734/","https://mixkit.co/free-stock-video/clouds-passing-across-the-sun-20734/")</f>
       </c>
       <c r="E11" s="0" t="inlineStr">
@@ -929,15 +685,12 @@
           <t xml:space="preserve">Outdoor reference (empty sky)</t>
         </is>
       </c>
-      <c r="F11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="0">
-        <v>11</v>
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
@@ -949,7 +702,7 @@
           <t xml:space="preserve">Desert/cactus + clouds</t>
         </is>
       </c>
-      <c r="D12" s="3" t="str">
+      <c r="D12" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/clouds-travel-along-the-blue-sky-in-the-presence-of-50136/","https://mixkit.co/free-stock-video/clouds-travel-along-the-blue-sky-in-the-presence-of-50136/")</f>
       </c>
       <c r="E12" s="0" t="inlineStr">
@@ -957,15 +710,12 @@
           <t xml:space="preserve">Outdoor reference (empty sky)</t>
         </is>
       </c>
-      <c r="F12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="0">
-        <v>12</v>
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
@@ -977,7 +727,7 @@
           <t xml:space="preserve">Sky reflecting on a building</t>
         </is>
       </c>
-      <c r="D13" s="3" t="str">
+      <c r="D13" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/time-lapse-of-sky-reflecting-on-a-building-101379/","https://mixkit.co/free-stock-video/time-lapse-of-sky-reflecting-on-a-building-101379/")</f>
       </c>
       <c r="E13" s="0" t="inlineStr">
@@ -985,15 +735,12 @@
           <t xml:space="preserve">Outdoor reference (empty sky)</t>
         </is>
       </c>
-      <c r="F13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="0">
-        <v>13</v>
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
@@ -1005,7 +752,7 @@
           <t xml:space="preserve">Cloudy sky timelapse</t>
         </is>
       </c>
-      <c r="D14" s="3" t="str">
+      <c r="D14" s="0" t="str">
         <f>HYPERLINK("https://coverr.co/videos/cloudy-sky-2v00ohjpqe","https://coverr.co/videos/cloudy-sky-2v00ohjpqe")</f>
       </c>
       <c r="E14" s="0" t="inlineStr">
@@ -1013,15 +760,12 @@
           <t xml:space="preserve">Outdoor reference (empty sky)</t>
         </is>
       </c>
-      <c r="F14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="0">
-        <v>14</v>
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
@@ -1033,7 +777,7 @@
           <t xml:space="preserve">Clouds moving during the day</t>
         </is>
       </c>
-      <c r="D15" s="3" t="str">
+      <c r="D15" s="0" t="str">
         <f>HYPERLINK("https://coverr.co/videos/timelapse-of-clouds-dsal4pxnyw","https://coverr.co/videos/timelapse-of-clouds-dsal4pxnyw")</f>
       </c>
       <c r="E15" s="0" t="inlineStr">
@@ -1041,15 +785,12 @@
           <t xml:space="preserve">Outdoor reference (empty sky)</t>
         </is>
       </c>
-      <c r="F15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="0">
-        <v>15</v>
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
@@ -1061,7 +802,7 @@
           <t xml:space="preserve">Clouds + bright blue sky</t>
         </is>
       </c>
-      <c r="D16" s="3" t="str">
+      <c r="D16" s="0" t="str">
         <f>HYPERLINK("https://coverr.co/videos/timelapse-of-the-clouds-oj4mcuuvzl","https://coverr.co/videos/timelapse-of-the-clouds-oj4mcuuvzl")</f>
       </c>
       <c r="E16" s="0" t="inlineStr">
@@ -1069,15 +810,12 @@
           <t xml:space="preserve">Outdoor reference (empty sky)</t>
         </is>
       </c>
-      <c r="F16" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" s="0">
-        <v>16</v>
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
@@ -1089,7 +827,7 @@
           <t xml:space="preserve">Blue sky + clouds timelapse</t>
         </is>
       </c>
-      <c r="D17" s="3" t="str">
+      <c r="D17" s="0" t="str">
         <f>HYPERLINK("https://www.pexels.com/video/serene-timelapse-of-blue-sky-with-clouds-29461557/","https://www.pexels.com/video/serene-timelapse-of-blue-sky-with-clouds-29461557/")</f>
       </c>
       <c r="E17" s="0" t="inlineStr">
@@ -1097,15 +835,12 @@
           <t xml:space="preserve">Outdoor reference (empty sky)</t>
         </is>
       </c>
-      <c r="F17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="0">
-        <v>17</v>
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17</t>
+        </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
@@ -1117,7 +852,7 @@
           <t xml:space="preserve">White clouds on blue sky</t>
         </is>
       </c>
-      <c r="D18" s="3" t="str">
+      <c r="D18" s="0" t="str">
         <f>HYPERLINK("https://www.pexels.com/video/serene-white-clouds-against-a-blue-sky-33545030/","https://www.pexels.com/video/serene-white-clouds-against-a-blue-sky-33545030/")</f>
       </c>
       <c r="E18" s="0" t="inlineStr">
@@ -1125,15 +860,12 @@
           <t xml:space="preserve">Outdoor reference (empty sky)</t>
         </is>
       </c>
-      <c r="F18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" s="0">
-        <v>18</v>
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18</t>
+        </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
@@ -1145,7 +877,7 @@
           <t xml:space="preserve">Cirrus clouds over a field</t>
         </is>
       </c>
-      <c r="D19" s="3" t="str">
+      <c r="D19" s="0" t="str">
         <f>HYPERLINK("https://www.pexels.com/video/vast-open-sky-with-cirrus-clouds-over-dry-field-32573013/","https://www.pexels.com/video/vast-open-sky-with-cirrus-clouds-over-dry-field-32573013/")</f>
       </c>
       <c r="E19" s="0" t="inlineStr">
@@ -1153,15 +885,12 @@
           <t xml:space="preserve">Outdoor reference (empty sky)</t>
         </is>
       </c>
-      <c r="F19" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="0">
-        <v>19</v>
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19</t>
+        </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
@@ -1173,36 +902,29 @@
           <t xml:space="preserve">Aerial cloudscape (check: no actual birds)</t>
         </is>
       </c>
-      <c r="D20" s="3" t="str">
+      <c r="D20" s="0" t="str">
         <f>HYPERLINK("https://www.pexels.com/video/cloudscape-in-birds-eye-view-12278365/","https://www.pexels.com/video/cloudscape-in-birds-eye-view-12278365/")</f>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outdoor reference (empty sky) — verify no birds</t>
-        </is>
-      </c>
-      <c r="F20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Outdoor reference — verify no birds</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F20"/>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:E20"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="36" customWidth="1"/>
-    <col min="5" max="5" width="70" customWidth="1"/>
-    <col min="6" max="6" width="36" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1236,15 +958,12 @@
           <t xml:space="preserve">Use as</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Downloaded?</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="0">
-        <v>1</v>
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
@@ -1261,7 +980,7 @@
           <t xml:space="preserve">Indoor house look</t>
         </is>
       </c>
-      <c r="E2" s="3" t="str">
+      <c r="E2" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/modern-living-room-with-wooden-furniture-3090/","https://mixkit.co/free-stock-video/modern-living-room-with-wooden-furniture-3090/")</f>
       </c>
       <c r="F2" s="0" t="inlineStr">
@@ -1269,15 +988,12 @@
           <t xml:space="preserve">Indoor reference (empty room)</t>
         </is>
       </c>
-      <c r="G2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="0">
-        <v>2</v>
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
@@ -1294,7 +1010,7 @@
           <t xml:space="preserve">Perch / fly-across space</t>
         </is>
       </c>
-      <c r="E3" s="3" t="str">
+      <c r="E3" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/minimalist-room-with-gray-sofa-3110/","https://mixkit.co/free-stock-video/minimalist-room-with-gray-sofa-3110/")</f>
       </c>
       <c r="F3" s="0" t="inlineStr">
@@ -1302,15 +1018,12 @@
           <t xml:space="preserve">Indoor reference (empty room)</t>
         </is>
       </c>
-      <c r="G3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="0">
-        <v>3</v>
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
@@ -1327,7 +1040,7 @@
           <t xml:space="preserve">Window = inside vs outside</t>
         </is>
       </c>
-      <c r="E4" s="3" t="str">
+      <c r="E4" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/minimalist-room-with-wooden-furniture-3091/","https://mixkit.co/free-stock-video/minimalist-room-with-wooden-furniture-3091/")</f>
       </c>
       <c r="F4" s="0" t="inlineStr">
@@ -1335,15 +1048,12 @@
           <t xml:space="preserve">Indoor reference (empty room)</t>
         </is>
       </c>
-      <c r="G4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="0">
-        <v>4</v>
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
@@ -1360,7 +1070,7 @@
           <t xml:space="preserve">Strong in-the-house cue</t>
         </is>
       </c>
-      <c r="E5" s="3" t="str">
+      <c r="E5" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/minimalist-room-with-a-couple-of-beds-3109/","https://mixkit.co/free-stock-video/minimalist-room-with-a-couple-of-beds-3109/")</f>
       </c>
       <c r="F5" s="0" t="inlineStr">
@@ -1368,15 +1078,12 @@
           <t xml:space="preserve">Indoor reference (empty room)</t>
         </is>
       </c>
-      <c r="G5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="0">
-        <v>5</v>
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
@@ -1393,7 +1100,7 @@
           <t xml:space="preserve">Indoor + view outside</t>
         </is>
       </c>
-      <c r="E6" s="3" t="str">
+      <c r="E6" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/master-bedroom-and-window-3111/","https://mixkit.co/free-stock-video/master-bedroom-and-window-3111/")</f>
       </c>
       <c r="F6" s="0" t="inlineStr">
@@ -1401,15 +1108,12 @@
           <t xml:space="preserve">Indoor reference (empty room)</t>
         </is>
       </c>
-      <c r="G6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="0">
-        <v>6</v>
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
@@ -1426,7 +1130,7 @@
           <t xml:space="preserve">Second indoor room type</t>
         </is>
       </c>
-      <c r="E7" s="3" t="str">
+      <c r="E7" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/interior-view-of-a-spacious-modern-kitchen-43033/","https://mixkit.co/free-stock-video/interior-view-of-a-spacious-modern-kitchen-43033/")</f>
       </c>
       <c r="F7" s="0" t="inlineStr">
@@ -1434,15 +1138,12 @@
           <t xml:space="preserve">Indoor reference (empty room)</t>
         </is>
       </c>
-      <c r="G7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="0">
-        <v>7</v>
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1160,7 @@
           <t xml:space="preserve">Bird can sit on sill / fly in</t>
         </is>
       </c>
-      <c r="E8" s="3" t="str">
+      <c r="E8" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/hotel-room-with-modern-minimalist-style-4488/","https://mixkit.co/free-stock-video/hotel-room-with-modern-minimalist-style-4488/")</f>
       </c>
       <c r="F8" s="0" t="inlineStr">
@@ -1467,15 +1168,12 @@
           <t xml:space="preserve">Indoor reference (empty room)</t>
         </is>
       </c>
-      <c r="G8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="0">
-        <v>8</v>
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
@@ -1492,7 +1190,7 @@
           <t xml:space="preserve">Slow camera through a room</t>
         </is>
       </c>
-      <c r="E9" s="3" t="str">
+      <c r="E9" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/luxury-hotel-room-panning-shot-4196/","https://mixkit.co/free-stock-video/luxury-hotel-room-panning-shot-4196/")</f>
       </c>
       <c r="F9" s="0" t="inlineStr">
@@ -1500,15 +1198,12 @@
           <t xml:space="preserve">Indoor reference (empty room)</t>
         </is>
       </c>
-      <c r="G9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="0">
-        <v>9</v>
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
@@ -1525,7 +1220,7 @@
           <t xml:space="preserve">Another indoor layout</t>
         </is>
       </c>
-      <c r="E10" s="3" t="str">
+      <c r="E10" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/pan-shot-of-the-interior-of-a-hotel-room-4198/","https://mixkit.co/free-stock-video/pan-shot-of-the-interior-of-a-hotel-room-4198/")</f>
       </c>
       <c r="F10" s="0" t="inlineStr">
@@ -1533,15 +1228,12 @@
           <t xml:space="preserve">Indoor reference (empty room)</t>
         </is>
       </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="0">
-        <v>10</v>
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
@@ -1558,7 +1250,7 @@
           <t xml:space="preserve">Bright indoor space</t>
         </is>
       </c>
-      <c r="E11" s="3" t="str">
+      <c r="E11" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/white-luxury-boutique-hotel-room-4046/","https://mixkit.co/free-stock-video/white-luxury-boutique-hotel-room-4046/")</f>
       </c>
       <c r="F11" s="0" t="inlineStr">
@@ -1566,15 +1258,12 @@
           <t xml:space="preserve">Indoor reference (empty room)</t>
         </is>
       </c>
-      <c r="G11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="0">
-        <v>11</v>
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
@@ -1591,7 +1280,7 @@
           <t xml:space="preserve">Living/sleep mix</t>
         </is>
       </c>
-      <c r="E12" s="3" t="str">
+      <c r="E12" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/hotel-room-with-breakfast-served-4019/","https://mixkit.co/free-stock-video/hotel-room-with-breakfast-served-4019/")</f>
       </c>
       <c r="F12" s="0" t="inlineStr">
@@ -1599,15 +1288,12 @@
           <t xml:space="preserve">Indoor reference (empty room)</t>
         </is>
       </c>
-      <c r="G12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="0">
-        <v>12</v>
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
@@ -1624,7 +1310,7 @@
           <t xml:space="preserve">Indoor, then opening out</t>
         </is>
       </c>
-      <c r="E13" s="3" t="str">
+      <c r="E13" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/beautifully-decorated-hotel-room-4030/","https://mixkit.co/free-stock-video/beautifully-decorated-hotel-room-4030/")</f>
       </c>
       <c r="F13" s="0" t="inlineStr">
@@ -1632,15 +1318,12 @@
           <t xml:space="preserve">Indoor reference (empty room)</t>
         </is>
       </c>
-      <c r="G13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="0">
-        <v>13</v>
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
@@ -1657,7 +1340,7 @@
           <t xml:space="preserve">Different furniture style</t>
         </is>
       </c>
-      <c r="E14" s="3" t="str">
+      <c r="E14" s="0" t="str">
         <f>HYPERLINK("https://mixkit.co/free-stock-video/vintage-living-room-setup-100891/","https://mixkit.co/free-stock-video/vintage-living-room-setup-100891/")</f>
       </c>
       <c r="F14" s="0" t="inlineStr">
@@ -1665,15 +1348,12 @@
           <t xml:space="preserve">Indoor reference (empty room)</t>
         </is>
       </c>
-      <c r="G14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="0">
-        <v>14</v>
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
@@ -1690,7 +1370,7 @@
           <t xml:space="preserve">Window to outside</t>
         </is>
       </c>
-      <c r="E15" s="3" t="str">
+      <c r="E15" s="0" t="str">
         <f>HYPERLINK("https://coverr.co/videos/contemporary-home-interior-with-scenic-view","https://coverr.co/videos/contemporary-home-interior-with-scenic-view")</f>
       </c>
       <c r="F15" s="0" t="inlineStr">
@@ -1698,15 +1378,12 @@
           <t xml:space="preserve">Indoor reference (empty room)</t>
         </is>
       </c>
-      <c r="G15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="0">
-        <v>15</v>
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
@@ -1723,7 +1400,7 @@
           <t xml:space="preserve">Empty-room reference</t>
         </is>
       </c>
-      <c r="E16" s="3" t="str">
+      <c r="E16" s="0" t="str">
         <f>HYPERLINK("https://coverr.co/videos/empty-minimal-gallery-space-with-polished-concrete-floor","https://coverr.co/videos/empty-minimal-gallery-space-with-polished-concrete-floor")</f>
       </c>
       <c r="F16" s="0" t="inlineStr">
@@ -1731,15 +1408,12 @@
           <t xml:space="preserve">Indoor reference (empty room)</t>
         </is>
       </c>
-      <c r="G16" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" s="0">
-        <v>16</v>
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
@@ -1756,7 +1430,7 @@
           <t xml:space="preserve">House interior</t>
         </is>
       </c>
-      <c r="E17" s="3" t="str">
+      <c r="E17" s="0" t="str">
         <f>HYPERLINK("https://pixabay.com/videos/cozy-fantasy-livingroom-apartment-176358/","https://pixabay.com/videos/cozy-fantasy-livingroom-apartment-176358/")</f>
       </c>
       <c r="F17" s="0" t="inlineStr">
@@ -1764,15 +1438,12 @@
           <t xml:space="preserve">Indoor reference (empty room)</t>
         </is>
       </c>
-      <c r="G17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="0">
-        <v>17</v>
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17</t>
+        </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
@@ -1789,7 +1460,7 @@
           <t xml:space="preserve">Sky seen FROM INSIDE</t>
         </is>
       </c>
-      <c r="E18" s="3" t="str">
+      <c r="E18" s="0" t="str">
         <f>HYPERLINK("https://pixabay.com/videos/cloud-window-sky-advertisement-110924/","https://pixabay.com/videos/cloud-window-sky-advertisement-110924/")</f>
       </c>
       <c r="F18" s="0" t="inlineStr">
@@ -1797,15 +1468,12 @@
           <t xml:space="preserve">Indoor reference (window to sky)</t>
         </is>
       </c>
-      <c r="G18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" s="0">
-        <v>18</v>
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18</t>
+        </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
@@ -1822,7 +1490,7 @@
           <t xml:space="preserve">Indoor looking out</t>
         </is>
       </c>
-      <c r="E19" s="3" t="str">
+      <c r="E19" s="0" t="str">
         <f>HYPERLINK("https://pixabay.com/videos/window-clouds-rain-roses-sky-city-12380/","https://pixabay.com/videos/window-clouds-rain-roses-sky-city-12380/")</f>
       </c>
       <c r="F19" s="0" t="inlineStr">
@@ -1830,742 +1498,1825 @@
           <t xml:space="preserve">Indoor reference (window to sky)</t>
         </is>
       </c>
-      <c r="G19" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G19"/>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:F19"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="70" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="36" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">What you want</t>
+          <t xml:space="preserve">#</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search terms</t>
+          <t xml:space="preserve">Source</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">What it is</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Link</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Approx. size</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notes</t>
+          <t xml:space="preserve">Use as</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">More empty sky</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">blue sky, clouds timelapse, clear sky</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="str">
-        <f>HYPERLINK("https://mixkit.co/free-stock-video/blue-sky/","https://mixkit.co/free-stock-video/blue-sky/")</f>
-      </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">~489</t>
-        </is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eagle gliding in a clear sky, bottom view</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/eagle-gliding-in-a-clear-sky-bottom-view-1706/","https://mixkit.co/free-stock-video/eagle-gliding-in-a-clear-sky-bottom-view-1706/")</f>
       </c>
       <c r="E2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skip any bird / eagle / flock</t>
+          <t xml:space="preserve">Outdoor TARGET (bird in sky)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">More clouds</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">cloud, cloudy</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="str">
-        <f>HYPERLINK("https://mixkit.co/free-stock-video/cloud/","https://mixkit.co/free-stock-video/cloud/")</f>
-      </c>
-      <c r="D3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">~1561</t>
-        </is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eagle flying high above the treetops</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/eagle-flying-high-above-the-tree-tops-6825/","https://mixkit.co/free-stock-video/eagle-flying-high-above-the-tree-tops-6825/")</f>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skip any bird / eagle / flock</t>
+          <t xml:space="preserve">Outdoor TARGET (bird in sky)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">All sky</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">sky</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="str">
-        <f>HYPERLINK("https://mixkit.co/free-stock-video/sky/","https://mixkit.co/free-stock-video/sky/")</f>
-      </c>
-      <c r="D4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">~2063</t>
-        </is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flock of seagulls in the sky</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/flock-of-seagulls-in-the-sky-17978/","https://mixkit.co/free-stock-video/flock-of-seagulls-in-the-sky-17978/")</f>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skip eagle / flock / bird</t>
+          <t xml:space="preserve">Outdoor TARGET (birds in sky)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">More clouds</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">clouds</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="str">
-        <f>HYPERLINK("https://mixkit.co/free-stock-video/clouds/","https://mixkit.co/free-stock-video/clouds/")</f>
-      </c>
-      <c r="D5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seagull flying across the sky</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/seagull-flying-across-the-sky-101185/","https://mixkit.co/free-stock-video/seagull-flying-across-the-sky-101185/")</f>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skip any bird / eagle / flock</t>
+          <t xml:space="preserve">Outdoor TARGET (bird in sky)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coverr sky</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">sky</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="str">
-        <f>HYPERLINK("https://coverr.co/stock-video-footage/sky","https://coverr.co/stock-video-footage/sky")</f>
-      </c>
-      <c r="D6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seagulls flying against the wind</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/seagulls-flying-against-the-wind-15298/","https://mixkit.co/free-stock-video/seagulls-flying-against-the-wind-15298/")</f>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Royalty-free; mix of real and AI</t>
+          <t xml:space="preserve">Outdoor TARGET (birds in sky)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coverr blue sky</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">blue sky</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="str">
-        <f>HYPERLINK("https://coverr.co/stock-video-footage/blue-sky","https://coverr.co/stock-video-footage/blue-sky")</f>
-      </c>
-      <c r="D7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seagulls flying over a lagoon</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/seagulls-flying-over-lagoon-101191/","https://mixkit.co/free-stock-video/seagulls-flying-over-lagoon-101191/")</f>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Royalty-free; mix of real and AI</t>
+          <t xml:space="preserve">Outdoor TARGET (birds in sky)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pexels sky</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">blue sky</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="str">
-        <f>HYPERLINK("https://www.pexels.com/search/videos/blue%20sky/","https://www.pexels.com/search/videos/blue%20sky/")</f>
-      </c>
-      <c r="D8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seagulls flying over the sky at sunset</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/seagulls-flying-over-the-sky-at-sunset-9317/","https://mixkit.co/free-stock-video/seagulls-flying-over-the-sky-at-sunset-9317/")</f>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Free to use</t>
+          <t xml:space="preserve">Outdoor TARGET (birds in sky)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pexels clouds</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">clouds timelapse</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="str">
-        <f>HYPERLINK("https://www.pexels.com/search/videos/clouds%20timelapse/","https://www.pexels.com/search/videos/clouds%20timelapse/")</f>
-      </c>
-      <c r="D9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flock of seagulls flying at sunset</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/flock-of-seagulls-flying-across-the-sky-with-a-sunset-45582/","https://mixkit.co/free-stock-video/flock-of-seagulls-flying-across-the-sky-with-a-sunset-45582/")</f>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Free to use</t>
+          <t xml:space="preserve">Outdoor TARGET (birds in sky)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pixabay sky</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">blue sky clouds</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="str">
-        <f>HYPERLINK("https://pixabay.com/videos/search/blue%20sky%20clouds/","https://pixabay.com/videos/search/blue%20sky%20clouds/")</f>
-      </c>
-      <c r="D10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flocks of birds flying in the sky</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/flocks-of-birds-flying-in-the-sky-9782/","https://mixkit.co/free-stock-video/flocks-of-birds-flying-in-the-sky-9782/")</f>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pixabay Content License</t>
+          <t xml:space="preserve">Outdoor TARGET (birds in sky)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pixabay sky</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">sky timelapse</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="str">
-        <f>HYPERLINK("https://pixabay.com/videos/search/sky%20timelapse/","https://pixabay.com/videos/search/sky%20timelapse/")</f>
-      </c>
-      <c r="D11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flock of birds over an urban lake</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/flock-of-birds-over-urban-lake-101383/","https://mixkit.co/free-stock-video/flock-of-birds-over-urban-lake-101383/")</f>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pixabay Content License</t>
+          <t xml:space="preserve">Outdoor TARGET (birds in sky)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Living rooms</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">living room</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="str">
-        <f>HYPERLINK("https://mixkit.co/free-stock-video/living-room/","https://mixkit.co/free-stock-video/living-room/")</f>
-      </c>
-      <c r="D12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">~310</t>
-        </is>
+          <t xml:space="preserve">Coverr</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seagulls flying around a bright blue sky</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="str">
+        <f>HYPERLINK("https://coverr.co/videos/seagulls-flying-around-rwaafdzlmj","https://coverr.co/videos/seagulls-flying-around-rwaafdzlmj")</f>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skip clips of people on the sofa</t>
+          <t xml:space="preserve">Outdoor TARGET (birds in sky)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hotel / bedroom</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">hotel room</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="str">
-        <f>HYPERLINK("https://mixkit.co/free-stock-video/hotel-room/","https://mixkit.co/free-stock-video/hotel-room/")</f>
-      </c>
-      <c r="D13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
+          <t xml:space="preserve">Coverr</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flock of birds in the sky</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="str">
+        <f>HYPERLINK("https://coverr.co/videos/flock-of-birds-in-the-sky-9d6jsspywm","https://coverr.co/videos/flock-of-birds-in-the-sky-9d6jsspywm")</f>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prefer empty rooms with windows</t>
+          <t xml:space="preserve">Outdoor TARGET (birds in sky)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interiors</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">interior</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="str">
-        <f>HYPERLINK("https://mixkit.co/free-stock-video/interior/","https://mixkit.co/free-stock-video/interior/")</f>
-      </c>
-      <c r="D14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">~125</t>
-        </is>
+          <t xml:space="preserve">Coverr</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pigeons flying away</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="str">
+        <f>HYPERLINK("https://coverr.co/videos/pigeons-flying-away-tfvshulwvu","https://coverr.co/videos/pigeons-flying-away-tfvshulwvu")</f>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prefer empty rooms with windows</t>
+          <t xml:space="preserve">Outdoor TARGET (birds flying)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Any room</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">room</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="str">
-        <f>HYPERLINK("https://mixkit.co/free-stock-video/room/","https://mixkit.co/free-stock-video/room/")</f>
-      </c>
-      <c r="D15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">~1086</t>
-        </is>
+          <t xml:space="preserve">Coverr</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seagulls flying on the coast</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="str">
+        <f>HYPERLINK("https://coverr.co/videos/seagulls-on-the-coast-4xknqopzsq","https://coverr.co/videos/seagulls-on-the-coast-4xknqopzsq")</f>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skip people-heavy clips</t>
+          <t xml:space="preserve">Outdoor TARGET (birds in sky)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minimal rooms</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">minimalist</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="str">
-        <f>HYPERLINK("https://mixkit.co/free-stock-video/minimalist/","https://mixkit.co/free-stock-video/minimalist/")</f>
-      </c>
-      <c r="D16" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">~107</t>
-        </is>
+          <t xml:space="preserve">Coverr</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rainbow lorikeet perched against blue sky</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="str">
+        <f>HYPERLINK("https://coverr.co/videos/vibrant-rainbow-lorikeet-perched-against-blue-sky","https://coverr.co/videos/vibrant-rainbow-lorikeet-perched-against-blue-sky")</f>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Good empty-room candidates</t>
+          <t xml:space="preserve">Outdoor TARGET (bird + sky)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Window shots</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">window</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="str">
-        <f>HYPERLINK("https://mixkit.co/free-stock-video/window/","https://mixkit.co/free-stock-video/window/")</f>
-      </c>
-      <c r="D17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
+          <t xml:space="preserve">Pexels</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flock of pigeons flying outdoors</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="str">
+        <f>HYPERLINK("https://www.pexels.com/video/a-flock-of-pigeons-are-flying-around-a-dirt-road-18334417/","https://www.pexels.com/video/a-flock-of-pigeons-are-flying-around-a-dirt-road-18334417/")</f>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Window teaches inside vs outside</t>
+          <t xml:space="preserve">Outdoor TARGET (birds flying)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Empty rooms</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty room</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="str">
-        <f>HYPERLINK("https://coverr.co/stock-video-footage/empty-room","https://coverr.co/stock-video-footage/empty-room")</f>
-      </c>
-      <c r="D18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
+          <t xml:space="preserve">Pixabay</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird swarm / flock in clouds</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="str">
+        <f>HYPERLINK("https://pixabay.com/videos/birds-swarm-flock-of-birds-clouds-184151/","https://pixabay.com/videos/birds-swarm-flock-of-birds-clouds-184151/")</f>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Royalty-free</t>
+          <t xml:space="preserve">Outdoor TARGET (birds in sky)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Empty living room</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty living room</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="str">
-        <f>HYPERLINK("https://www.pexels.com/search/videos/empty%20living%20room/","https://www.pexels.com/search/videos/empty%20living%20room/")</f>
-      </c>
-      <c r="D19" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
+          <t xml:space="preserve">Pixabay</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird flock, forest animals</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="str">
+        <f>HYPERLINK("https://pixabay.com/videos/birds-flock-animals-forest-174316/","https://pixabay.com/videos/birds-flock-animals-forest-174316/")</f>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Best indoor references</t>
+          <t xml:space="preserve">Outdoor TARGET (birds flying)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Empty bedroom</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty bedroom</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="str">
-        <f>HYPERLINK("https://www.pexels.com/search/videos/empty%20bedroom/","https://www.pexels.com/search/videos/empty%20bedroom/")</f>
-      </c>
-      <c r="D20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
+          <t xml:space="preserve">Pixabay</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seagulls, wings, flying in sky</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="str">
+        <f>HYPERLINK("https://pixabay.com/videos/seagulls-birds-wings-marine-49948/","https://pixabay.com/videos/seagulls-birds-wings-marine-49948/")</f>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indoor variety</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Room + window</t>
-        </is>
-      </c>
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">living room window</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="str">
-        <f>HYPERLINK("https://www.pexels.com/search/videos/living%20room%20window/","https://www.pexels.com/search/videos/living%20room%20window/")</f>
-      </c>
-      <c r="D21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Window = bird is inside the house</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kitchen</t>
-        </is>
-      </c>
-      <c r="B22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kitchen interior</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="str">
-        <f>HYPERLINK("https://www.pexels.com/search/videos/kitchen%20interior/","https://www.pexels.com/search/videos/kitchen%20interior/")</f>
-      </c>
-      <c r="D22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Indoor variety</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pixabay living room</t>
-        </is>
-      </c>
-      <c r="B23" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty living room</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="str">
-        <f>HYPERLINK("https://pixabay.com/videos/search/empty%20living%20room/","https://pixabay.com/videos/search/empty%20living%20room/")</f>
-      </c>
-      <c r="D23" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E23" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Skip people</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pixabay living room</t>
-        </is>
-      </c>
-      <c r="B24" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">elegant living room design</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="str">
-        <f>HYPERLINK("https://pixabay.com/videos/search/elegant%20living%20room%20design/","https://pixabay.com/videos/search/elegant%20living%20room%20design/")</f>
-      </c>
-      <c r="D24" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E24" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Skip people</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pixabay kitchen</t>
-        </is>
-      </c>
-      <c r="B25" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">modern kitchen interior</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="str">
-        <f>HYPERLINK("https://pixabay.com/videos/search/modern%20kitchen%20interior/","https://pixabay.com/videos/search/modern%20kitchen%20interior/")</f>
-      </c>
-      <c r="D25" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E25" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Indoor variety</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pixabay bedroom</t>
-        </is>
-      </c>
-      <c r="B26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bedroom interior</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="str">
-        <f>HYPERLINK("https://pixabay.com/videos/search/bedroom%20interior/","https://pixabay.com/videos/search/bedroom%20interior/")</f>
-      </c>
-      <c r="D26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Indoor variety</t>
+          <t xml:space="preserve">Outdoor TARGET (birds in sky)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E26"/>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:E20"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="46" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
-    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pair name</t>
+          <t xml:space="preserve">#</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reference from</t>
+          <t xml:space="preserve">Source</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Target you still need</t>
+          <t xml:space="preserve">What it is</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teaches</t>
+          <t xml:space="preserve">Setting</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Link</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Use as</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sky bird</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Empty Sky Clips tab</t>
+          <t xml:space="preserve">Mixkit</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Same sky WITH bird flying</t>
+          <t xml:space="preserve">Canary scratching its head in a cage</t>
         </is>
       </c>
       <c r="D2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bird outdoors</t>
+          <t xml:space="preserve">Indoor cage / pet bird</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/canary-scratching-its-head-in-a-cage-26730/","https://mixkit.co/free-stock-video/canary-scratching-its-head-in-a-cage-26730/")</f>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indoor TARGET (bird inside)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Macaw parrot feeding on a branch, in captivity</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Captivity / pet-like</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/macaw-parrot-feeding-on-a-branch-4669/","https://mixkit.co/free-stock-video/macaw-parrot-feeding-on-a-branch-4669/")</f>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird identity / indoor-adjacent TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parrot eating, close up</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Close identity shot</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/parrot-eating-close-up-7094/","https://mixkit.co/free-stock-video/parrot-eating-close-up-7094/")</f>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird identity TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Close up of a parrot in nature</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perched parrot</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/close-up-of-a-parrot-in-nature-14363/","https://mixkit.co/free-stock-video/close-up-of-a-parrot-in-nature-14363/")</f>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird identity TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chattering parrot eating on a tree branch</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perched parrot</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/chattering-parrot-eating-on-a-tree-branch-48849/","https://mixkit.co/free-stock-video/chattering-parrot-eating-on-a-tree-branch-48849/")</f>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird identity TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parrot eating on a tree branch</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perched parrot</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/parrot-eating-in-a-tree-branch-7177/","https://mixkit.co/free-stock-video/parrot-eating-in-a-tree-branch-7177/")</f>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird identity TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vibrant red parrot eating fruit on a tree</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perched parrot</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/vibrant-red-parrot-eating-fruit-on-a-tree-48848/","https://mixkit.co/free-stock-video/vibrant-red-parrot-eating-fruit-on-a-tree-48848/")</f>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird identity TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parrot eating sugar cane</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perched parrot</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/parrot-eating-a-sugar-cane-6866/","https://mixkit.co/free-stock-video/parrot-eating-a-sugar-cane-6866/")</f>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird identity TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yellow bird on a tree branch (sanctuary)</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perched small bird</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/yellow-bird-on-tree-branch-4666/","https://mixkit.co/free-stock-video/yellow-bird-on-tree-branch-4666/")</f>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird identity TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Birds singing in a tree</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perched birds</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/birds-singing-in-a-tree-20512/","https://mixkit.co/free-stock-video/birds-singing-in-a-tree-20512/")</f>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird identity TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mixkit</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rooster inside its cage looking at camera</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cage (not a house bird, but indoor cage)</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/rooster-inside-its-cage-looking-at-the-camera-49044/","https://mixkit.co/free-stock-video/rooster-inside-its-cage-looking-at-the-camera-49044/")</f>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indoor cage TARGET (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pexels</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Close-up video of a parrot / macaw</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identity close-up</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="str">
+        <f>HYPERLINK("https://www.pexels.com/video/a-close-up-video-of-a-parrot-10041594/","https://www.pexels.com/video/a-close-up-video-of-a-parrot-10041594/")</f>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird identity TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pexels</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Green parrot on a tree branch</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perched parrot</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="str">
+        <f>HYPERLINK("https://www.pexels.com/video/a-green-parrot-on-a-tree-branch-12715051/","https://www.pexels.com/video/a-green-parrot-on-a-tree-branch-12715051/")</f>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird identity TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pixabay</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gray parrot close-up</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pet parrot look</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="str">
+        <f>HYPERLINK("https://pixabay.com/videos/bird-gray-parrot-parrot-animal-131650/","https://pixabay.com/videos/bird-gray-parrot-parrot-animal-131650/")</f>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird identity / indoor-adjacent TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pixabay</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nature parrot</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perched parrot</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="str">
+        <f>HYPERLINK("https://pixabay.com/videos/nature-bird-parrot-armenia-21862/","https://pixabay.com/videos/nature-bird-parrot-armenia-21862/")</f>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird identity TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pixabay</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parrot on a tree</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perched parrot</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="str">
+        <f>HYPERLINK("https://pixabay.com/videos/parrot-bird-tree-nature-ave-green-21309/","https://pixabay.com/videos/parrot-bird-tree-nature-ave-green-21309/")</f>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird identity TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pixabay</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colorful bird / parrot</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perched parrot</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="str">
+        <f>HYPERLINK("https://pixabay.com/videos/bird-animal-colorful-guatica-25509/","https://pixabay.com/videos/bird-animal-colorful-guatica-25509/")</f>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird identity TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pixabay</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird parrot colorful</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perched parrot</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="str">
+        <f>HYPERLINK("https://pixabay.com/videos/bird-parrot-nature-animal-colorful-46026/","https://pixabay.com/videos/bird-parrot-nature-animal-colorful-46026/")</f>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird identity TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pixabay</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parrot, banana, tree, avian</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perched parrot</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="str">
+        <f>HYPERLINK("https://pixabay.com/videos/parrot-bird-banana-tree-avian-87068/","https://pixabay.com/videos/parrot-bird-banana-tree-avian-87068/")</f>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird identity TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pixabay</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nature parrot on a tree</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perched parrot</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="str">
+        <f>HYPERLINK("https://pixabay.com/videos/nature-ave-parrot-bird-tree-22229/","https://pixabay.com/videos/nature-ave-parrot-bird-tree-22229/")</f>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird identity TARGET</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F21"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What you want</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Search terms</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Link</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Approx. size</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">More empty sky</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blue sky, clouds timelapse, clear sky</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/blue-sky/","https://mixkit.co/free-stock-video/blue-sky/")</f>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~489</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skip any bird / eagle / flock</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">More clouds</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cloud, cloudy</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/cloud/","https://mixkit.co/free-stock-video/cloud/")</f>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~1561</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skip any bird / eagle / flock</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All sky</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sky</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/sky/","https://mixkit.co/free-stock-video/sky/")</f>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~2063</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skip eagle / flock / bird if you need EMPTY sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coverr sky</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sky</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="str">
+        <f>HYPERLINK("https://coverr.co/stock-video-footage/sky","https://coverr.co/stock-video-footage/sky")</f>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Royalty-free</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pexels sky</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blue sky</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="str">
+        <f>HYPERLINK("https://www.pexels.com/search/videos/blue%20sky/","https://www.pexels.com/search/videos/blue%20sky/")</f>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free to use</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pixabay sky</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blue sky clouds</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="str">
+        <f>HYPERLINK("https://pixabay.com/videos/search/blue%20sky%20clouds/","https://pixabay.com/videos/search/blue%20sky%20clouds/")</f>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pixabay Content License</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Living rooms</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">living room</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/living-room/","https://mixkit.co/free-stock-video/living-room/")</f>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~310</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skip clips of people on the sofa</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hotel / bedroom</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hotel room</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/hotel-room/","https://mixkit.co/free-stock-video/hotel-room/")</f>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prefer empty rooms with windows</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Empty living room</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty living room</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="str">
+        <f>HYPERLINK("https://www.pexels.com/search/videos/empty%20living%20room/","https://www.pexels.com/search/videos/empty%20living%20room/")</f>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Best indoor references</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Room + window</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">living room window</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="str">
+        <f>HYPERLINK("https://www.pexels.com/search/videos/living%20room%20window/","https://www.pexels.com/search/videos/living%20room%20window/")</f>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Window = bird is inside the house</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mixkit birds (499 clips)</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">birds</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/birds/","https://mixkit.co/free-stock-video/birds/")</f>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~499</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main bird TARGET dump</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mixkit bird</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bird</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/bird/","https://mixkit.co/free-stock-video/bird/")</f>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~499</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same library, bird tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mixkit parrot (21 clips)</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parrot</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="str">
+        <f>HYPERLINK("https://mixkit.co/free-stock-video/parrot/","https://mixkit.co/free-stock-video/parrot/")</f>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~21</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Good identity / perched birds</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pexels flying birds</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flying birds</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="str">
+        <f>HYPERLINK("https://www.pexels.com/search/videos/flying%20birds/","https://www.pexels.com/search/videos/flying%20birds/")</f>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thousands</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outdoor TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pexels parrot</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parrot</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="str">
+        <f>HYPERLINK("https://www.pexels.com/search/videos/parrot/","https://www.pexels.com/search/videos/parrot/")</f>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identity TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pexels pigeon</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pigeon flying</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="str">
+        <f>HYPERLINK("https://www.pexels.com/search/videos/pigeon%20flying/","https://www.pexels.com/search/videos/pigeon%20flying/")</f>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outdoor TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pixabay birds flying</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">birds flying</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="str">
+        <f>HYPERLINK("https://pixabay.com/videos/search/birds%20flying/","https://pixabay.com/videos/search/birds%20flying/")</f>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thousands</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outdoor TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pixabay parrot</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parrot</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="str">
+        <f>HYPERLINK("https://pixabay.com/videos/search/parrot/","https://pixabay.com/videos/search/parrot/")</f>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identity / pet bird</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pixabay indoor parrot</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parrot indoor</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="str">
+        <f>HYPERLINK("https://pixabay.com/videos/search/parrot%20indoor/","https://pixabay.com/videos/search/parrot%20indoor/")</f>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hunt for house-bird TARGETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pixabay pet bird</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pet bird cage</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="str">
+        <f>HYPERLINK("https://pixabay.com/videos/search/pet%20bird%20cage/","https://pixabay.com/videos/search/pet%20bird%20cage/")</f>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indoor TARGET candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pixabay green screen flying birds</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">green screen birds flying</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="str">
+        <f>HYPERLINK("https://pixabay.com/videos/search/green%20screen%20birds%20flying/","https://pixabay.com/videos/search/green%20screen%20birds%20flying/")</f>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Useful to composite a bird into empty rooms/sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coverr birds</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bird</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="str">
+        <f>HYPERLINK("https://coverr.co/stock-video-footage/bird","https://coverr.co/stock-video-footage/bird")</f>
+      </c>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outdoor TARGET</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E23"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pair name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reference from</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target from</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teaches</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky bird</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Empty Sky Clips tab</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird videos (sky / flying) tab</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird outdoors in the sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">House bird</t>
         </is>
       </c>
@@ -2576,7 +3327,7 @@
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAME room WITH bird on furniture / flying inside</t>
+          <t xml:space="preserve">Bird videos (parrot / cage / perch) + your own indoor filming or composite</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
@@ -2585,8 +3336,29 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identity</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Any clean close parrot/bird clip</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same bird in many scenes</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same bird look across rooms and sky</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D3"/>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:D4"/>
 </worksheet>
 </file>